--- a/Element/Element.xlsx
+++ b/Element/Element.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Elin\Package\Mod_PandaWizardHarvestMod\Element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F308E-33DD-48BD-816F-716BF3F20937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DA9116-6E24-4EFA-A3A9-1532DD2FD892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -303,7 +303,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>10</t>
+    <t>46</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1061,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P4" s="9" t="s">
         <v>78</v>
@@ -1069,8 +1069,8 @@
       <c r="Q4" s="8">
         <v>320</v>
       </c>
-      <c r="R4" s="8">
-        <v>12</v>
+      <c r="R4" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="S4" s="8"/>
       <c r="T4" s="5"/>
@@ -1151,8 +1151,8 @@
       <c r="Q5" s="8">
         <v>320</v>
       </c>
-      <c r="R5" s="8">
-        <v>12</v>
+      <c r="R5" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="5"/>
